--- a/DS_HS2026_LNW_I_Examples/AP03/bicycle_data.xlsx
+++ b/DS_HS2026_LNW_I_Examples/AP03/bicycle_data.xlsx
@@ -41349,7 +41349,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Eindeutige Fahrrad-ID; kein Modellmerkmal</t>
+          <t>Eindeutige Velo-ID; kein Feature</t>
         </is>
       </c>
     </row>
@@ -41417,7 +41417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1 = E-Bike; 0 = konventionelles Fahrrad</t>
+          <t>1 = E-Bike; 0 = konventionelles Velo</t>
         </is>
       </c>
     </row>
@@ -41485,7 +41485,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Regressionsziel: später erzielter Verkaufspreis</t>
+          <t>Target (Regression): später erzielter Verkaufspreis</t>
         </is>
       </c>
     </row>
@@ -41502,7 +41502,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Klassifikationsziel: anschliessender Werkstattentscheid; 1 = Service nötig</t>
+          <t>Target (Classification): anschliessender Werkstattentscheid; 1 = Service nötig</t>
         </is>
       </c>
     </row>
@@ -41557,7 +41557,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>generate_bicycle_data.py; NumPy default_rng; Seed 42; 1200 Fahrräder</t>
+          <t>generate_bicycle_data.py; NumPy default_rng; Seed 42; 1200 Velos</t>
         </is>
       </c>
     </row>
@@ -41569,7 +41569,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Merkmale bei Eingang; Zielwerte werden erst danach beobachtet</t>
+          <t>Features bei Eingang; Targets werden erst danach beobachtet</t>
         </is>
       </c>
     </row>
@@ -41605,7 +41605,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Lehrdaten; die Güte ist kein Nachweis für die Leistung auf realen Fahrraddaten</t>
+          <t>Lehrdaten; die Performance ist kein Nachweis für die Leistung auf realen Velodaten</t>
         </is>
       </c>
     </row>
